--- a/ig/DM-MAI-2025/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
+++ b/ig/DM-MAI-2025/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-16T08:21:48+00:00</t>
+    <t>2025-05-21T08:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MAI-2025/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
+++ b/ig/DM-MAI-2025/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T08:10:15+00:00</t>
+    <t>2025-05-22T08:23:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
